--- a/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed2val/score_seed2val.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed2val/score_seed2val.xlsx
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.7098953524161281</v>
+        <v>0.7099030470914127</v>
       </c>
       <c r="E164" t="n">
         <v>0.883183568677792</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.693674976915974</v>
+        <v>0.6936749769159742</v>
       </c>
       <c r="E188" t="n">
         <v>0.8767650834403081</v>
@@ -16241,13 +16241,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr"/>
+      <c r="D452" t="n">
+        <v>0.7309018159433671</v>
+      </c>
+      <c r="E452" t="n">
+        <v>0.865211810012837</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0.3863636363636364</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0.1789473684210526</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.2446043165467626</v>
+      </c>
       <c r="I452" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
     </row>
     <row r="453">
@@ -16266,13 +16276,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr"/>
+      <c r="D453" t="n">
+        <v>0.74070536630231</v>
+      </c>
+      <c r="E453" t="n">
+        <v>0.8767650834403081</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0.1728395061728395</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0.2258064516129032</v>
+      </c>
       <c r="I453" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
     </row>
     <row r="454">
@@ -16291,13 +16311,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
+      <c r="D454" t="n">
+        <v>0.7461465323362162</v>
+      </c>
+      <c r="E454" t="n">
+        <v>0.8236994219653179</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0.2816901408450704</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0.2197802197802198</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0.2469135802469136</v>
+      </c>
       <c r="I454" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="455">
@@ -16316,13 +16346,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
+      <c r="D455" t="n">
+        <v>0.7874705203472327</v>
+      </c>
+      <c r="E455" t="n">
+        <v>0.7861271676300579</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0.4901960784313725</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0.3424657534246575</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0.4032258064516129</v>
+      </c>
       <c r="I455" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="456">
@@ -16341,13 +16381,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
+      <c r="D456" t="n">
+        <v>0.8033347959631417</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0.7572254335260116</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0.6113744075829384</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0.6056338028169014</v>
+      </c>
       <c r="I456" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="457">
@@ -16366,13 +16416,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
+      <c r="D457" t="n">
+        <v>0.8559701492537314</v>
+      </c>
+      <c r="E457" t="n">
+        <v>0.9725433526011561</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0.5128205128205128</v>
+      </c>
       <c r="I457" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="458">
@@ -17126,13 +17186,23 @@
           <t>Layered</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
-      <c r="H479" t="inlineStr"/>
+      <c r="D479" t="n">
+        <v>0.7492222389482663</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0.7687861271676301</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0.4794520547945205</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0.4666666666666667</v>
+      </c>
       <c r="I479" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="480">
@@ -17151,13 +17221,23 @@
           <t>Layered</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
+      <c r="D480" t="n">
+        <v>0.8025791038954707</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0.7572254335260116</v>
+      </c>
+      <c r="F480" t="n">
+        <v>0.6312849162011173</v>
+      </c>
+      <c r="G480" t="n">
+        <v>0.5255813953488372</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0.5736040609137056</v>
+      </c>
       <c r="I480" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="481">
